--- a/astro-site/public/dl/restaurant-financial-plan-templates/01b-restaurant-financial-projections-5-year.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/01b-restaurant-financial-projections-5-year.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -225,6 +225,9 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -235,6 +238,9 @@
     <xf numFmtId="4" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -792,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B23"/>
+  <dimension ref="A2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -904,6 +910,13 @@
       <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1047,43 +1060,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -1094,43 +1107,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -1141,43 +1154,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -1188,43 +1201,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -1235,55 +1248,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -1301,43 +1314,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -1348,43 +1361,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -1395,43 +1408,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -1442,55 +1455,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -1501,43 +1514,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -1548,43 +1561,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -1595,43 +1608,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -1642,43 +1655,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -1689,55 +1702,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -1764,55 +1777,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -1883,8 +1896,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -2060,43 +2073,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -2107,43 +2120,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -2154,43 +2167,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -2201,43 +2214,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -2248,55 +2261,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -2314,43 +2327,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -2361,43 +2374,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -2408,43 +2421,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -2455,55 +2468,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -2514,43 +2527,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -2561,43 +2574,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -2608,43 +2621,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -2655,43 +2668,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -2702,55 +2715,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -2777,55 +2790,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -2896,8 +2909,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -3073,43 +3086,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -3120,43 +3133,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -3167,43 +3180,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -3214,43 +3227,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -3261,55 +3274,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -3327,43 +3340,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -3374,43 +3387,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -3421,43 +3434,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -3468,55 +3481,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -3527,43 +3540,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -3574,43 +3587,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -3621,43 +3634,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -3668,43 +3681,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -3715,55 +3728,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -3790,55 +3803,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -3909,8 +3922,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -4086,43 +4099,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -4133,43 +4146,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -4180,43 +4193,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -4227,43 +4240,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -4274,55 +4287,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -4340,43 +4353,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -4387,43 +4400,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -4434,43 +4447,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -4481,55 +4494,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -4540,43 +4553,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -4587,43 +4600,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -4634,43 +4647,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -4681,43 +4694,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -4728,55 +4741,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -4803,55 +4816,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -4922,8 +4935,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -5099,43 +5112,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -5146,43 +5159,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -5193,43 +5206,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -5240,43 +5253,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -5287,55 +5300,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -5353,43 +5366,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -5400,43 +5413,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -5447,43 +5460,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -5494,55 +5507,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -5553,43 +5566,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -5600,43 +5613,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -5647,43 +5660,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -5694,43 +5707,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -5741,55 +5754,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -5816,55 +5829,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -5935,8 +5948,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -6063,23 +6076,23 @@
           <t>Total Revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="32">
         <f>'Year 1'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="32">
         <f>'Year 2'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="32">
         <f>'Year 3'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="32">
         <f>'Year 4'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="32">
         <f>'Year 5'!N10</f>
         <v>0.0</v>
       </c>
@@ -6094,23 +6107,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="32">
         <f>'Year 1'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="32">
         <f>'Year 2'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <f>'Year 3'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="32">
         <f>'Year 4'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="32">
         <f>'Year 5'!N21</f>
         <v>0.0</v>
       </c>
@@ -6125,23 +6138,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="32">
         <f>'Year 1'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="32">
         <f>'Year 2'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="32">
         <f>'Year 3'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="32">
         <f>'Year 4'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="32">
         <f>'Year 5'!N23</f>
         <v>0.0</v>
       </c>
